--- a/livrables/documents/2026-10-22_Les 8 Jobs.xlsx
+++ b/livrables/documents/2026-10-22_Les 8 Jobs.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-10-22_Les 8 Jobs.xlsx
+++ b/livrables/documents/2026-10-22_Les 8 Jobs.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
